--- a/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 3,03</t>
+          <t>-0,7; 3,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 3,76</t>
+          <t>-0,33; 3,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 7,38</t>
+          <t>0,54; 7,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 3,37</t>
+          <t>-1,64; 3,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 0,83</t>
+          <t>-3,63; 0,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 7,74</t>
+          <t>0,03; 7,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,65</t>
+          <t>-0,56; 2,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,64</t>
+          <t>-1,2; 1,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,04</t>
+          <t>0,82; 6,12</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 362,0</t>
+          <t>-38,86; 334,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 488,2</t>
+          <t>-21,43; 425,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 805,85</t>
+          <t>-2,76; 766,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,51; 144,64</t>
+          <t>-40,58; 147,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,41; 40,19</t>
+          <t>-75,77; 40,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-12,08; 316,62</t>
+          <t>-9,4; 300,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 147,46</t>
+          <t>-20,17; 131,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,92; 99,39</t>
+          <t>-42,1; 85,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 320,74</t>
+          <t>28,02; 341,82</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,98</t>
+          <t>0,82; 4,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,55</t>
+          <t>-0,89; 2,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,47</t>
+          <t>3,74; 12,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,74</t>
+          <t>-0,62; 3,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,43</t>
+          <t>-1,85; 1,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,6</t>
+          <t>-1,5; 2,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,52</t>
+          <t>0,7; 3,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,45</t>
+          <t>-0,88; 1,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,95</t>
+          <t>1,57; 6,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,33; 289,37</t>
+          <t>22,28; 332,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-34,04; 171,9</t>
+          <t>-33,28; 157,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122,95; 758,39</t>
+          <t>124,34; 758,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-14,56; 233,58</t>
+          <t>-21,6; 214,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 86,98</t>
+          <t>-55,34; 114,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,35; 138,05</t>
+          <t>-46,5; 160,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,57; 196,82</t>
+          <t>19,64; 185,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 78,27</t>
+          <t>-30,94; 89,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,1; 302,67</t>
+          <t>51,14; 306,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 3,46</t>
+          <t>-1,47; 3,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,47</t>
+          <t>-2,89; 1,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 2,01</t>
+          <t>-3,07; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 5,49</t>
+          <t>-0,09; 5,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,21</t>
+          <t>-2,86; 1,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,09</t>
+          <t>-1,83; 3,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 3,79</t>
+          <t>0,27; 3,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 0,94</t>
+          <t>-2,24; 0,79</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,85</t>
+          <t>-1,47; 1,79</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 115,45</t>
+          <t>-27,41; 115,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,54; 58,3</t>
+          <t>-51,51; 64,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-52,59; 65,16</t>
+          <t>-54,08; 66,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,54; 150,87</t>
+          <t>-2,74; 154,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,52; 41,97</t>
+          <t>-49,71; 42,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-29,05; 89,98</t>
+          <t>-33,15; 90,11</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 112,16</t>
+          <t>4,31; 104,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-44,04; 28,93</t>
+          <t>-42,26; 24,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 50,47</t>
+          <t>-28,25; 48,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 4,25</t>
+          <t>-1,78; 4,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,98</t>
+          <t>-1,07; 4,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 6,21</t>
+          <t>-3,82; 6,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 4,9</t>
+          <t>-2,36; 4,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 1,69</t>
+          <t>-5,04; 1,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 3,46</t>
+          <t>-2,56; 3,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 3,67</t>
+          <t>-1,04; 3,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 2,1</t>
+          <t>-2,12; 2,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 3,71</t>
+          <t>-2,59; 3,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 112,42</t>
+          <t>-26,46; 108,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,45; 129,71</t>
+          <t>-15,07; 125,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,85; 132,51</t>
+          <t>-50,5; 132,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 76,09</t>
+          <t>-22,12; 78,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,69; 27,0</t>
+          <t>-46,68; 30,29</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,41; 52,98</t>
+          <t>-24,45; 47,91</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 64,37</t>
+          <t>-12,33; 59,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,9; 38,17</t>
+          <t>-26,17; 40,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 59,13</t>
+          <t>-33,32; 60,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 6,1</t>
+          <t>-2,46; 5,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 3,36</t>
+          <t>-4,31; 3,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 11,18</t>
+          <t>2,67; 10,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 7,72</t>
+          <t>-0,69; 7,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,17</t>
+          <t>0,91; 9,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 5,71</t>
+          <t>-1,35; 5,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 5,56</t>
+          <t>-0,26; 5,57</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,62</t>
+          <t>-0,35; 5,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,2</t>
+          <t>1,76; 7,46</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 85,86</t>
+          <t>-25,12; 81,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,65; 46,36</t>
+          <t>-39,37; 51,31</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22,44; 166,31</t>
+          <t>23,11; 167,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 130,67</t>
+          <t>-10,01; 122,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,99; 152,41</t>
+          <t>8,63; 152,39</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 104,9</t>
+          <t>-14,34; 103,3</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 77,63</t>
+          <t>-2,49; 79,51</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 79,5</t>
+          <t>-5,22; 76,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>17,0; 103,49</t>
+          <t>15,82; 104,85</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 10,93</t>
+          <t>-0,31; 10,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 3,33</t>
+          <t>-5,13; 3,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,24; 8,91</t>
+          <t>0,66; 8,95</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 6,95</t>
+          <t>-1,91; 7,34</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 3,29</t>
+          <t>-4,65; 3,42</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,2; 67,04</t>
+          <t>3,93; 63,87</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 7,23</t>
+          <t>0,21; 7,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 2,18</t>
+          <t>-3,64; 2,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,36; 54,29</t>
+          <t>4,07; 54,69</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 171,21</t>
+          <t>-1,12; 173,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,73; 56,83</t>
+          <t>-46,57; 63,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0,14; 135,71</t>
+          <t>4,47; 144,58</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 104,34</t>
+          <t>-17,15; 108,97</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 47,67</t>
+          <t>-42,46; 52,88</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>43,79; 1093,92</t>
+          <t>39,69; 963,74</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,53; 99,26</t>
+          <t>1,25; 95,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-36,16; 29,53</t>
+          <t>-35,35; 30,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>46,02; 739,07</t>
+          <t>42,94; 752,33</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 11,56</t>
+          <t>-1,85; 10,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 0,46</t>
+          <t>-9,56; 1,19</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,57; 20,79</t>
+          <t>9,03; 21,43</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,21; 12,45</t>
+          <t>1,44; 13,18</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 7,09</t>
+          <t>-3,81; 7,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,44; 23,31</t>
+          <t>13,17; 23,23</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,99</t>
+          <t>1,57; 9,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 3,24</t>
+          <t>-4,92; 3,04</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,0; 20,91</t>
+          <t>13,29; 20,92</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 130,91</t>
+          <t>-13,91; 125,54</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 9,28</t>
+          <t>-64,25; 17,02</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>60,84; 238,93</t>
+          <t>57,47; 259,64</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7,77; 131,61</t>
+          <t>10,34; 132,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 69,04</t>
+          <t>-25,91; 72,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>81,79; 239,24</t>
+          <t>79,17; 247,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,94; 96,71</t>
+          <t>11,43; 95,5</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-30,97; 28,99</t>
+          <t>-33,57; 29,51</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>86,75; 204,02</t>
+          <t>88,99; 208,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,57</t>
+          <t>1,02; 3,39</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,64</t>
+          <t>-0,78; 1,62</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,96</t>
+          <t>3,22; 6,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,12</t>
+          <t>1,48; 4,19</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,8</t>
+          <t>-0,58; 1,92</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,17; 25,27</t>
+          <t>4,22; 24,02</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,41</t>
+          <t>1,74; 3,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,41</t>
+          <t>-0,29; 1,46</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,62; 17,2</t>
+          <t>4,66; 15,84</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>21,43; 79,23</t>
+          <t>17,2; 76,62</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-10,62; 37,67</t>
+          <t>-13,72; 36,56</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>58,69; 154,49</t>
+          <t>62,04; 154,33</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22,25; 73,1</t>
+          <t>20,45; 73,41</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 31,97</t>
+          <t>-8,84; 33,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>64,01; 422,49</t>
+          <t>66,08; 418,22</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,21; 66,27</t>
+          <t>28,35; 67,2</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 27,01</t>
+          <t>-4,87; 27,8</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>79,18; 323,21</t>
+          <t>80,62; 298,72</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>3,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,21</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 3,07</t>
+          <t>-0,65; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 3,75</t>
+          <t>-0,37; 3,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,15</t>
+          <t>0,26; 6,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,33</t>
+          <t>-1,78; 3,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,74</t>
+          <t>-3,45; 0,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,03; 7,87</t>
+          <t>-0,22; 7,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,47</t>
+          <t>-0,68; 2,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,63</t>
+          <t>-1,31; 1,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,82; 6,12</t>
+          <t>0,66; 5,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>208,03%</t>
+          <t>188,17%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100,51%</t>
+          <t>104,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>132,07%</t>
+          <t>130,17%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 334,14</t>
+          <t>-37,28; 385,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-21,43; 425,77</t>
+          <t>-30,45; 460,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 766,1</t>
+          <t>0,42; 760,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,58; 147,83</t>
+          <t>-38,91; 147,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 40,9</t>
+          <t>-75,22; 43,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,4; 300,13</t>
+          <t>-5,4; 335,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,17; 131,4</t>
+          <t>-24,15; 146,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,1; 85,79</t>
+          <t>-41,36; 97,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28,02; 341,82</t>
+          <t>17,65; 296,07</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,37</t>
+          <t>6,24</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>1,48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,64</t>
+          <t>3,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,92</t>
+          <t>0,77; 4,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,48</t>
+          <t>-0,89; 2,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,12</t>
+          <t>3,24; 10,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 3,65</t>
+          <t>-0,58; 3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,74</t>
+          <t>-1,87; 1,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,68</t>
+          <t>-0,71; 3,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,63</t>
+          <t>0,85; 3,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,61</t>
+          <t>-0,83; 1,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,17</t>
+          <t>1,91; 6,24</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>326,11%</t>
+          <t>275,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>153,65%</t>
+          <t>160,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,28; 332,44</t>
+          <t>20,63; 294,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 157,92</t>
+          <t>-33,59; 169,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124,34; 758,49</t>
+          <t>94,78; 631,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 214,38</t>
+          <t>-19,72; 216,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,34; 114,89</t>
+          <t>-58,07; 99,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 160,32</t>
+          <t>-27,66; 203,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,64; 185,14</t>
+          <t>25,59; 197,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,94; 89,15</t>
+          <t>-31,14; 92,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>51,14; 306,16</t>
+          <t>54,99; 305,55</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,68</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>1,25</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 3,65</t>
+          <t>-1,37; 3,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,66</t>
+          <t>-2,86; 1,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,91</t>
+          <t>-3,07; 1,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,4</t>
+          <t>-0,04; 5,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,55</t>
+          <t>-3,07; 1,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 3,19</t>
+          <t>-1,18; 3,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,84</t>
+          <t>0,07; 3,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,79</t>
+          <t>-2,16; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 1,79</t>
+          <t>-1,33; 1,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-13,37%</t>
+          <t>-16,28%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 115,69</t>
+          <t>-25,32; 126,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-51,51; 64,98</t>
+          <t>-52,84; 50,08</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-54,08; 66,23</t>
+          <t>-56,72; 52,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 154,71</t>
+          <t>-4,6; 152,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,71; 42,82</t>
+          <t>-52,61; 42,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,15; 90,11</t>
+          <t>-21,76; 104,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,31; 104,98</t>
+          <t>1,46; 103,31</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,26; 24,08</t>
+          <t>-42,11; 29,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 48,61</t>
+          <t>-25,9; 54,3</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,17</t>
+          <t>4,8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,23</t>
+          <t>2,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,21</t>
+          <t>-1,59; 4,13</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,58</t>
+          <t>-1,27; 4,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 6,15</t>
+          <t>1,77; 7,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,89</t>
+          <t>-2,29; 4,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 1,78</t>
+          <t>-4,87; 1,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,1</t>
+          <t>-1,97; 3,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 3,41</t>
+          <t>-1,04; 3,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,28</t>
+          <t>-2,22; 2,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 3,82</t>
+          <t>0,72; 4,92</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 108,53</t>
+          <t>-23,92; 104,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 125,36</t>
+          <t>-20,23; 113,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 132,33</t>
+          <t>20,21; 189,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 78,69</t>
+          <t>-22,58; 69,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 30,29</t>
+          <t>-47,2; 24,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,45; 47,91</t>
+          <t>-19,27; 60,57</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 59,35</t>
+          <t>-13,2; 65,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,17; 40,33</t>
+          <t>-28,08; 38,15</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-33,32; 60,58</t>
+          <t>8,53; 84,19</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7,0</t>
+          <t>6,56</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,83</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 5,86</t>
+          <t>-2,62; 6,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 3,5</t>
+          <t>-4,18; 3,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,87</t>
+          <t>2,38; 10,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 7,86</t>
+          <t>-0,84; 7,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 9,03</t>
+          <t>0,36; 9,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,74</t>
+          <t>-0,65; 6,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,57</t>
+          <t>-0,31; 5,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,42</t>
+          <t>-0,75; 5,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,76; 7,46</t>
+          <t>2,08; 7,4</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 81,79</t>
+          <t>-24,47; 83,05</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 51,31</t>
+          <t>-37,26; 50,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,11; 167,78</t>
+          <t>18,01; 155,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 122,53</t>
+          <t>-9,35; 124,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,63; 152,39</t>
+          <t>2,53; 157,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 103,3</t>
+          <t>-6,73; 103,93</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 79,51</t>
+          <t>-4,57; 82,93</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 76,99</t>
+          <t>-7,66; 73,53</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,82; 104,85</t>
+          <t>20,68; 107,75</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4,94</t>
+          <t>4,85</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>34,3</t>
+          <t>5,71</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23,26</t>
+          <t>5,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 10,22</t>
+          <t>0,17; 10,88</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,74</t>
+          <t>-5,13; 3,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 8,95</t>
+          <t>0,34; 8,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 7,34</t>
+          <t>-2,03; 7,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,42</t>
+          <t>-4,78; 3,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,93; 63,87</t>
+          <t>1,43; 9,37</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,21; 7,11</t>
+          <t>0,42; 7,16</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,16</t>
+          <t>-3,54; 2,69</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,07; 54,69</t>
+          <t>2,38; 7,93</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>384,85%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>265,73%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 173,67</t>
+          <t>-0,98; 170,18</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 63,6</t>
+          <t>-46,77; 58,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,47; 144,58</t>
+          <t>1,26; 142,82</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 108,97</t>
+          <t>-19,38; 101,33</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-42,46; 52,88</t>
+          <t>-43,96; 48,01</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,69; 963,74</t>
+          <t>13,1; 136,33</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,25; 95,21</t>
+          <t>3,27; 95,1</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 30,21</t>
+          <t>-34,58; 36,73</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42,94; 752,33</t>
+          <t>21,82; 110,69</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15,12</t>
+          <t>14,74</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,63</t>
+          <t>18,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>17,22</t>
+          <t>17,12</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 10,95</t>
+          <t>-2,26; 10,51</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 1,19</t>
+          <t>-9,05; 0,87</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,03; 21,43</t>
+          <t>8,59; 20,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,18</t>
+          <t>0,91; 12,7</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 7,27</t>
+          <t>-4,24; 6,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,17; 23,23</t>
+          <t>13,9; 23,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,91</t>
+          <t>1,52; 10,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 3,04</t>
+          <t>-4,6; 3,26</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,29; 20,92</t>
+          <t>13,14; 20,81</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>129,17%</t>
+          <t>125,85%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>148,24%</t>
+          <t>149,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>140,73%</t>
+          <t>139,91%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 125,54</t>
+          <t>-16,32; 121,9</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-64,25; 17,02</t>
+          <t>-64,14; 11,85</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57,47; 259,64</t>
+          <t>52,07; 226,21</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>10,34; 132,11</t>
+          <t>4,86; 128,18</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-25,91; 72,26</t>
+          <t>-27,9; 67,78</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>79,17; 247,93</t>
+          <t>88,19; 256,37</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>11,43; 95,5</t>
+          <t>9,91; 97,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 29,51</t>
+          <t>-32,14; 30,98</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>88,99; 208,31</t>
+          <t>87,06; 210,62</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5,47</t>
+          <t>5,87</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,39</t>
+          <t>1,17; 3,55</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,62</t>
+          <t>-0,53; 1,65</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,95</t>
+          <t>4,52; 7,28</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,19</t>
+          <t>1,4; 4,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,92</t>
+          <t>-0,68; 1,68</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,22; 24,02</t>
+          <t>3,92; 6,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,56</t>
+          <t>1,69; 3,51</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,46</t>
+          <t>-0,17; 1,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,66; 15,84</t>
+          <t>4,63; 6,42</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>109,53%</t>
+          <t>117,5%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>151,36%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>134,04%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>17,2; 76,62</t>
+          <t>20,1; 77,28</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 36,56</t>
+          <t>-9,85; 36,58</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>62,04; 154,33</t>
+          <t>80,42; 164,08</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20,45; 73,41</t>
+          <t>20,11; 71,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 33,54</t>
+          <t>-10,08; 29,19</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>66,08; 418,22</t>
+          <t>56,55; 112,98</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>28,35; 67,2</t>
+          <t>27,45; 65,99</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 27,8</t>
+          <t>-2,75; 27,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>80,62; 298,72</t>
+          <t>77,09; 121,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2A_fisi_R-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad física</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad física</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
